--- a/Ütemterv.xlsx
+++ b/Ütemterv.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhasz.arnold.2022i_\Documents\Arnold\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhasz.arnold.2022i_\Documents\Arnold\Projekt\Library-Loan-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912AE2BA-5E9A-462B-9058-36DA3A793853}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC0D650-3DD4-4646-88D4-13B634431C0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{2016E0A9-1AAD-44EC-BA20-DEFD174A4FE2}"/>
   </bookViews>
@@ -180,6 +180,21 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -189,24 +204,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -214,10 +218,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -377,109 +377,6 @@
           <a:avLst>
             <a:gd name="adj1" fmla="val 75263"/>
           </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="Egyenes összekötő 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DFBF5B1-DE00-4F24-B412-28134A2B8AE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17145000" y="3952875"/>
-          <a:ext cx="0" cy="609600"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Egyenes összekötő nyíllal 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{272B0BF5-95C8-4E23-83B7-2F618504EF5C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="17154525" y="4562475"/>
-          <a:ext cx="1666875" cy="9525"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
         </a:prstGeom>
         <a:ln>
           <a:tailEnd type="triangle"/>
@@ -866,476 +763,484 @@
   </cols>
   <sheetData>
     <row r="1" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Y1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="16" t="s">
+      <c r="AF1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R2" s="6"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="6"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="6"/>
+      <c r="R2" s="3"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="3"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="6"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="6"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="6"/>
+      <c r="R3" s="3"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="3"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="3"/>
     </row>
     <row r="4" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="H4" s="2"/>
-      <c r="R4" s="6"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="6"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="6"/>
+      <c r="H4" s="11"/>
+      <c r="R4" s="3"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="3"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="3"/>
     </row>
     <row r="5" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R5" s="6"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="6"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="6"/>
+      <c r="R5" s="3"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="3"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="3"/>
     </row>
     <row r="6" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="8"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="6"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="6"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="9"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="3"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="3"/>
     </row>
     <row r="7" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="8"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="6"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="6"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="9"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="3"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="3"/>
     </row>
     <row r="8" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R8" s="6"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="6"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="6"/>
+      <c r="R8" s="3"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="3"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="3"/>
     </row>
     <row r="9" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="6"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="6"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="6"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="3"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="3"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="3"/>
     </row>
     <row r="10" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="6"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="6"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="9"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="6"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="3"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="3"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="3"/>
     </row>
     <row r="11" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R11" s="6"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="6"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="6"/>
+      <c r="R11" s="3"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="3"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="3"/>
     </row>
     <row r="12" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O12" s="3" t="s">
+      <c r="O12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="6"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="6"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="3"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="3"/>
     </row>
     <row r="13" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="6"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="6"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="3"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="3"/>
     </row>
     <row r="14" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R14" s="6"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="6"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="6"/>
+      <c r="R14" s="3"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="3"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="3"/>
     </row>
     <row r="15" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3"/>
-      <c r="R15" s="6"/>
-      <c r="V15" s="10" t="s">
+      <c r="P15" s="12"/>
+      <c r="R15" s="3"/>
+      <c r="V15" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="6"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="6"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="3"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="3"/>
     </row>
     <row r="16" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="R16" s="6"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="6"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="6"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="R16" s="3"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="3"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4"/>
+      <c r="AF16" s="3"/>
     </row>
     <row r="17" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R17" s="6"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="6"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-      <c r="AC17" s="9"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
-      <c r="AF17" s="6"/>
+      <c r="R17" s="3"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="3"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="3"/>
     </row>
     <row r="18" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="S18" s="3"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="10" t="s">
+      <c r="S18" s="12"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="11"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="6"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="15"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AF18" s="3"/>
     </row>
     <row r="19" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="11"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="6"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="15"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="3"/>
     </row>
     <row r="20" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R20" s="6"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="6"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="6"/>
+      <c r="R20" s="3"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="3"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="3"/>
     </row>
     <row r="21" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R21" s="6"/>
-      <c r="S21" s="3" t="s">
+      <c r="R21" s="3"/>
+      <c r="S21" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="T21" s="3"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="6"/>
+      <c r="T21" s="12"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="3"/>
       <c r="AA21" s="13" t="s">
         <v>5</v>
       </c>
       <c r="AB21" s="13"/>
       <c r="AC21" s="13"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="6"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="3"/>
     </row>
     <row r="22" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R22" s="6"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="6"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="3"/>
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="6"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="3"/>
     </row>
     <row r="23" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R23" s="6"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="6"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="6"/>
+      <c r="R23" s="3"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="3"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="3"/>
     </row>
     <row r="24" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R24" s="6"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="6"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="13" t="s">
+      <c r="R24" s="3"/>
+      <c r="T24" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AD24" s="13"/>
-      <c r="AE24" s="13"/>
-      <c r="AF24" s="6"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="3"/>
     </row>
     <row r="25" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R25" s="6"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="6"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
+      <c r="R25" s="3"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
       <c r="AC25" s="13"/>
-      <c r="AD25" s="13"/>
-      <c r="AE25" s="13"/>
-      <c r="AF25" s="6"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="3"/>
     </row>
     <row r="26" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R26" s="6"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="6"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-      <c r="AF26" s="6"/>
+      <c r="R26" s="3"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="3"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="3"/>
     </row>
     <row r="27" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R27" s="6"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="6"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="14" t="s">
+      <c r="R27" s="3"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="3"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="AE27" s="14"/>
-      <c r="AF27" s="15"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="17"/>
     </row>
     <row r="28" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R28" s="6"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="6"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="14"/>
-      <c r="AF28" s="15"/>
+      <c r="R28" s="3"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="3"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="17"/>
     </row>
     <row r="29" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R29" s="6"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="6"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
-      <c r="AD29" s="9"/>
-      <c r="AE29" s="9"/>
-      <c r="AF29" s="6"/>
+      <c r="R29" s="3"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="3"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="18:32" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="R30" s="17" t="s">
+      <c r="R30" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="17" t="s">
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="9"/>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="17" t="s">
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="7" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="W18:Y19"/>
+    <mergeCell ref="AD27:AF28"/>
+    <mergeCell ref="T24:AC25"/>
     <mergeCell ref="J6:R7"/>
     <mergeCell ref="M9:Q10"/>
     <mergeCell ref="H3:H4"/>
@@ -1345,11 +1250,9 @@
     <mergeCell ref="O15:P16"/>
     <mergeCell ref="S21:T22"/>
     <mergeCell ref="R18:S19"/>
-    <mergeCell ref="AC24:AE25"/>
-    <mergeCell ref="W18:Y19"/>
-    <mergeCell ref="AD27:AF28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Ütemterv.xlsx
+++ b/Ütemterv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhasz.arnold.2022i_\Documents\Arnold\Projekt\Library-Loan-System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhasz.arnold.2022i_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC0D650-3DD4-4646-88D4-13B634431C0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D1AF5E-8306-4B3C-9AE4-F1C36CF2F7FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{2016E0A9-1AAD-44EC-BA20-DEFD174A4FE2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{2016E0A9-1AAD-44EC-BA20-DEFD174A4FE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Projekt kezdete</t>
   </si>
@@ -66,15 +66,6 @@
     <t>2 új funkció</t>
   </si>
   <si>
-    <t>2025. november. 22</t>
-  </si>
-  <si>
-    <t>2025. december. 14</t>
-  </si>
-  <si>
-    <t>2026. január. 5.</t>
-  </si>
-  <si>
     <t>M1</t>
   </si>
   <si>
@@ -82,13 +73,37 @@
   </si>
   <si>
     <t>M3</t>
+  </si>
+  <si>
+    <t>2025. december 2.</t>
+  </si>
+  <si>
+    <t>2025. december 14.</t>
+  </si>
+  <si>
+    <t>2026. január 5.</t>
+  </si>
+  <si>
+    <t>2025. október 20.</t>
+  </si>
+  <si>
+    <t>2025. november 16.</t>
+  </si>
+  <si>
+    <t>2025. december 20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025. december 18. </t>
+  </si>
+  <si>
+    <t>2026. január 8.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +126,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -157,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -174,20 +198,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -204,19 +261,33 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -756,9 +827,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -766,71 +842,90 @@
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>15</v>
+      <c r="J1" s="13"/>
+      <c r="N1" s="2"/>
+      <c r="R1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" s="2"/>
+      <c r="AF1" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R2" s="3"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="3"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="3"/>
+      <c r="J2" s="13"/>
+      <c r="N2" s="2"/>
+      <c r="R2" s="18"/>
+      <c r="T2" s="2"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="18"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="18"/>
     </row>
     <row r="3" spans="8:32" x14ac:dyDescent="0.25">
       <c r="H3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="3"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="3"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="2"/>
+      <c r="R3" s="18"/>
+      <c r="T3" s="2"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="18"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="18"/>
     </row>
     <row r="4" spans="8:32" x14ac:dyDescent="0.25">
       <c r="H4" s="11"/>
-      <c r="R4" s="3"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="3"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="3"/>
+      <c r="J4" s="13"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="2"/>
+      <c r="R4" s="18"/>
+      <c r="T4" s="2"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="18"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="18"/>
     </row>
     <row r="5" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R5" s="3"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="3"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="3"/>
+      <c r="J5" s="13"/>
+      <c r="N5" s="2"/>
+      <c r="R5" s="18"/>
+      <c r="T5" s="2"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="18"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="18"/>
     </row>
     <row r="6" spans="8:32" x14ac:dyDescent="0.25">
       <c r="J6" s="8" t="s">
@@ -844,16 +939,17 @@
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="9"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="3"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="3"/>
+      <c r="T6" s="2"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="18"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="18"/>
     </row>
     <row r="7" spans="8:32" x14ac:dyDescent="0.25">
       <c r="J7" s="8"/>
@@ -865,31 +961,36 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="9"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="3"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="3"/>
+      <c r="T7" s="2"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="18"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="18"/>
     </row>
     <row r="8" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R8" s="3"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="3"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="3"/>
+      <c r="J8" s="13"/>
+      <c r="N8" s="2"/>
+      <c r="R8" s="18"/>
+      <c r="T8" s="2"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="18"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="18"/>
     </row>
     <row r="9" spans="8:32" x14ac:dyDescent="0.25">
+      <c r="J9" s="13"/>
       <c r="M9" s="10" t="s">
         <v>3</v>
       </c>
@@ -897,352 +998,435 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
-      <c r="R9" s="3"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="3"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
-      <c r="AF9" s="3"/>
+      <c r="R9" s="18"/>
+      <c r="T9" s="2"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="18"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="18"/>
     </row>
     <row r="10" spans="8:32" x14ac:dyDescent="0.25">
+      <c r="J10" s="13"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
-      <c r="R10" s="3"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="3"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="3"/>
+      <c r="R10" s="18"/>
+      <c r="T10" s="2"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="18"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="18"/>
     </row>
     <row r="11" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R11" s="3"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="3"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="2"/>
+      <c r="R11" s="18"/>
+      <c r="T11" s="2"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="18"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="18"/>
     </row>
     <row r="12" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O12" s="12" t="s">
+      <c r="J12" s="13"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="3"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="3"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="5"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="18"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="18"/>
     </row>
     <row r="13" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="3"/>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="5"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="18"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="18"/>
     </row>
     <row r="14" spans="8:32" x14ac:dyDescent="0.25">
-      <c r="R14" s="3"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="3"/>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="3"/>
+      <c r="J14" s="13"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="2"/>
+      <c r="R14" s="18"/>
+      <c r="T14" s="2"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="18"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="18"/>
     </row>
     <row r="15" spans="8:32" x14ac:dyDescent="0.25">
+      <c r="J15" s="13"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="2"/>
       <c r="O15" s="12" t="s">
         <v>10</v>
       </c>
       <c r="P15" s="12"/>
-      <c r="R15" s="3"/>
-      <c r="V15" s="14" t="s">
+      <c r="R15" s="18"/>
+      <c r="T15" s="2"/>
+      <c r="V15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="3"/>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
-      <c r="AF15" s="3"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="18"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="18"/>
     </row>
     <row r="16" spans="8:32" x14ac:dyDescent="0.25">
+      <c r="J16" s="13"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="2"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
-      <c r="R16" s="3"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="3"/>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R17" s="3"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="3"/>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
-      <c r="AF17" s="3"/>
-    </row>
-    <row r="18" spans="18:32" x14ac:dyDescent="0.25">
+      <c r="R16" s="18"/>
+      <c r="T16" s="2"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="18"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="18"/>
+    </row>
+    <row r="17" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J17" s="13"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="2"/>
+      <c r="R17" s="18"/>
+      <c r="T17" s="2"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="18"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="18"/>
+    </row>
+    <row r="18" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J18" s="13"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="2"/>
       <c r="R18" s="12" t="s">
         <v>12</v>
       </c>
       <c r="S18" s="12"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="14" t="s">
+      <c r="T18" s="2"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="15"/>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AF18" s="3"/>
-    </row>
-    <row r="19" spans="18:32" x14ac:dyDescent="0.25">
+      <c r="X18" s="4"/>
+      <c r="Y18" s="21"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="3"/>
+      <c r="AF18" s="18"/>
+    </row>
+    <row r="19" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J19" s="13"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="2"/>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="15"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R20" s="3"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="3"/>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="3"/>
-    </row>
-    <row r="21" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R21" s="3"/>
-      <c r="S21" s="12" t="s">
+      <c r="T19" s="2"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="21"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="18"/>
+    </row>
+    <row r="20" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J20" s="13"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="2"/>
+      <c r="R20" s="18"/>
+      <c r="T20" s="2"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="18"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="18"/>
+    </row>
+    <row r="21" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J21" s="13"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="2"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="T21" s="12"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="3"/>
-      <c r="AA21" s="13" t="s">
+      <c r="T21" s="5"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="18"/>
+      <c r="AA21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
-      <c r="AF21" s="3"/>
-    </row>
-    <row r="22" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R22" s="3"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="3"/>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
-      <c r="AC22" s="13"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
-      <c r="AF22" s="3"/>
-    </row>
-    <row r="23" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R23" s="3"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="3"/>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
-      <c r="AF23" s="3"/>
-    </row>
-    <row r="24" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R24" s="3"/>
-      <c r="T24" s="13" t="s">
+      <c r="AB21" s="7"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="18"/>
+    </row>
+    <row r="22" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J22" s="13"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="2"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="5"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="18"/>
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="18"/>
+    </row>
+    <row r="23" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J23" s="13"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="2"/>
+      <c r="R23" s="18"/>
+      <c r="T23" s="2"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="18"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="18"/>
+    </row>
+    <row r="24" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J24" s="13"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="2"/>
+      <c r="R24" s="18"/>
+      <c r="T24" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="13"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="13"/>
-      <c r="AB24" s="13"/>
-      <c r="AC24" s="13"/>
-      <c r="AD24" s="4"/>
-      <c r="AE24" s="4"/>
-      <c r="AF24" s="3"/>
-    </row>
-    <row r="25" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R25" s="3"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="13"/>
-      <c r="AB25" s="13"/>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="4"/>
-      <c r="AE25" s="4"/>
-      <c r="AF25" s="3"/>
-    </row>
-    <row r="26" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R26" s="3"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="3"/>
-      <c r="AA26" s="4"/>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
-      <c r="AF26" s="3"/>
-    </row>
-    <row r="27" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R27" s="3"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="3"/>
-      <c r="AA27" s="4"/>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
-      <c r="AD27" s="16" t="s">
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="18"/>
+    </row>
+    <row r="25" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J25" s="13"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="2"/>
+      <c r="R25" s="18"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="18"/>
+    </row>
+    <row r="26" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J26" s="13"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="2"/>
+      <c r="R26" s="18"/>
+      <c r="T26" s="2"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="18"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="18"/>
+    </row>
+    <row r="27" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J27" s="13"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="2"/>
+      <c r="R27" s="18"/>
+      <c r="T27" s="2"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="18"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="AE27" s="16"/>
-      <c r="AF27" s="17"/>
-    </row>
-    <row r="28" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R28" s="3"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="3"/>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="17"/>
-    </row>
-    <row r="29" spans="18:32" x14ac:dyDescent="0.25">
-      <c r="R29" s="3"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="3"/>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="3"/>
-    </row>
-    <row r="30" spans="18:32" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="R30" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="7" t="s">
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="27"/>
+    </row>
+    <row r="28" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J28" s="13"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="2"/>
+      <c r="R28" s="18"/>
+      <c r="T28" s="2"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="18"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="26"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="27"/>
+    </row>
+    <row r="29" spans="9:32" x14ac:dyDescent="0.25">
+      <c r="J29" s="13"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="2"/>
+      <c r="R29" s="18"/>
+      <c r="T29" s="2"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="18"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="18"/>
+    </row>
+    <row r="30" spans="9:32" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="I30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="14"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="T30" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="7" t="s">
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y30" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="W18:Y19"/>
-    <mergeCell ref="AD27:AF28"/>
-    <mergeCell ref="T24:AC25"/>
-    <mergeCell ref="J6:R7"/>
-    <mergeCell ref="M9:Q10"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="O12:T13"/>
     <mergeCell ref="AA21:AC22"/>
@@ -1250,6 +1434,11 @@
     <mergeCell ref="O15:P16"/>
     <mergeCell ref="S21:T22"/>
     <mergeCell ref="R18:S19"/>
+    <mergeCell ref="W18:Y19"/>
+    <mergeCell ref="AD27:AF28"/>
+    <mergeCell ref="T24:AC25"/>
+    <mergeCell ref="J6:R7"/>
+    <mergeCell ref="M9:Q10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
